--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488207_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488207_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.4639</v>
+        <v>7.7999</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0961</v>
+        <v>6.3582</v>
       </c>
       <c r="F2" t="n">
-        <v>1.3679</v>
+        <v>1.4417</v>
       </c>
       <c r="G2" t="n">
         <v>2.6257</v>
@@ -610,13 +610,13 @@
         <v>1.6676</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1236</v>
+        <v>0.2123</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2524</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1288</v>
+        <v>0.2027</v>
       </c>
       <c r="V2" t="n">
         <v>4.406</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.2753</v>
+        <v>4.0603</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3595</v>
+        <v>0.2183</v>
       </c>
       <c r="F3" t="n">
-        <v>3.9158</v>
+        <v>3.8419</v>
       </c>
       <c r="G3" t="n">
         <v>1.1747</v>
@@ -688,13 +688,13 @@
         <v>2.7793</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3213</v>
+        <v>0.1063</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6156</v>
+        <v>0.4744</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2942</v>
+        <v>-0.3681</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.8618</v>
+        <v>3.7152</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8762</v>
+        <v>1.6804</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9855</v>
+        <v>2.0348</v>
       </c>
       <c r="G4" t="n">
         <v>0.8151</v>
@@ -766,13 +766,13 @@
         <v>1.8529</v>
       </c>
       <c r="S4" t="n">
-        <v>0.5638</v>
+        <v>0.4172</v>
       </c>
       <c r="T4" t="n">
-        <v>0.725</v>
+        <v>0.5291</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1612</v>
+        <v>-0.1119</v>
       </c>
       <c r="V4" t="n">
         <v>0.63</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.0807</v>
+        <v>2.7141</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5577</v>
+        <v>1.068</v>
       </c>
       <c r="F5" t="n">
-        <v>1.523</v>
+        <v>1.6461</v>
       </c>
       <c r="G5" t="n">
         <v>0.7991</v>
@@ -844,13 +844,13 @@
         <v>2.2234</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3731</v>
+        <v>0.0065</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2684</v>
+        <v>0.7788</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8954</v>
+        <v>-0.7723</v>
       </c>
       <c r="V5" t="n">
         <v>-0.315</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ TORRERO</t>
+          <t>H. ANDRADE CORREIA E SILVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8269</v>
+        <v>1.7851</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0409</v>
+        <v>0.2648</v>
       </c>
       <c r="F6" t="n">
-        <v>2.8678</v>
+        <v>1.5203</v>
       </c>
       <c r="G6" t="n">
-        <v>4.1053</v>
+        <v>1.9904</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4617</v>
+        <v>2.052</v>
       </c>
       <c r="I6" t="n">
-        <v>1.6437</v>
+        <v>-0.0616</v>
       </c>
       <c r="J6" t="n">
-        <v>3.2806</v>
+        <v>1.0121</v>
       </c>
       <c r="K6" t="n">
-        <v>2.4819</v>
+        <v>2.2028</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7986</v>
+        <v>-1.1907</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8247</v>
+        <v>0.9782999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0203</v>
+        <v>-0.1508</v>
       </c>
       <c r="O6" t="n">
-        <v>0.845</v>
+        <v>1.1292</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.4087</v>
+        <v>1.6676</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.8175</v>
+        <v>-0.9264</v>
       </c>
       <c r="R6" t="n">
-        <v>2.4087</v>
+        <v>2.594</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1303</v>
+        <v>-0.2991</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1816</v>
+        <v>0.1797</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0513</v>
+        <v>-0.4788</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-1.5738</v>
       </c>
       <c r="W6" t="n">
-        <v>0.3144</v>
+        <v>-0.0005</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3144</v>
+        <v>-1.5733</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. GOMEZ MORENO</t>
+          <t>A. RODRIGUEZ TORRERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0867</v>
+        <v>1.7749</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2653</v>
+        <v>-0.822</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1785</v>
+        <v>2.5969</v>
       </c>
       <c r="G7" t="n">
-        <v>1.137</v>
+        <v>4.1053</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6853</v>
+        <v>2.4617</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4517</v>
+        <v>1.6437</v>
       </c>
       <c r="J7" t="n">
-        <v>1.1048</v>
+        <v>3.2806</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0219</v>
+        <v>2.4819</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0829</v>
+        <v>0.7986</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0322</v>
+        <v>0.8247</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3366</v>
+        <v>-0.0203</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3687</v>
+        <v>0.845</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.1853</v>
+        <v>-2.4087</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9264</v>
+        <v>-4.8175</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7411</v>
+        <v>2.4087</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0789</v>
+        <v>0.07829999999999999</v>
       </c>
       <c r="T7" t="n">
-        <v>1.0869</v>
+        <v>0.4004</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.008</v>
+        <v>-0.3221</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.9439</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9835</v>
+        <v>0.9589</v>
       </c>
       <c r="E8" t="n">
         <v>-1.0682</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0516</v>
+        <v>2.027</v>
       </c>
       <c r="G8" t="n">
         <v>1.1516</v>
@@ -1078,13 +1078,13 @@
         <v>2.2234</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5387</v>
+        <v>-0.5633</v>
       </c>
       <c r="T8" t="n">
         <v>0.1269</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.6656</v>
+        <v>-0.6902</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>H. ANDRADE CORREIA E SILVA</t>
+          <t>P. GOMEZ MORENO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9535</v>
+        <v>0.5161</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7145</v>
+        <v>0.7439</v>
       </c>
       <c r="F9" t="n">
-        <v>1.668</v>
+        <v>-0.2278</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9904</v>
+        <v>1.137</v>
       </c>
       <c r="H9" t="n">
-        <v>2.052</v>
+        <v>0.6853</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0616</v>
+        <v>0.4517</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0121</v>
+        <v>1.1048</v>
       </c>
       <c r="K9" t="n">
-        <v>2.2028</v>
+        <v>1.0219</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1907</v>
+        <v>0.0829</v>
       </c>
       <c r="M9" t="n">
-        <v>0.9782999999999999</v>
+        <v>0.0322</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1508</v>
+        <v>-0.3366</v>
       </c>
       <c r="O9" t="n">
-        <v>1.1292</v>
+        <v>0.3687</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6676</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>2.594</v>
+        <v>0.7411</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.1306</v>
+        <v>0.5083</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7996</v>
+        <v>0.5655</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3311</v>
+        <v>-0.0572</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.5738</v>
+        <v>-0.9439</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.0005</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.5733</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MURILLO PONS</t>
+          <t>A. ALVAREZ RICO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2091</v>
+        <v>-0.0408</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.484</v>
+        <v>-1.2639</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2749</v>
+        <v>1.2232</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2058</v>
+        <v>-0.3081</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2257</v>
+        <v>0.4614</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9801</v>
+        <v>-0.7695</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.2614</v>
+        <v>0.1816</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0644</v>
+        <v>0.7514999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.3258</v>
+        <v>-0.5699</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0556</v>
+        <v>-0.4897</v>
       </c>
       <c r="N10" t="n">
         <v>-0.2901</v>
       </c>
       <c r="O10" t="n">
-        <v>0.3457</v>
+        <v>-0.1996</v>
       </c>
       <c r="P10" t="n">
-        <v>0.5558999999999999</v>
+        <v>-1.297</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1117</v>
+        <v>-2.9646</v>
       </c>
       <c r="R10" t="n">
         <v>1.6676</v>
       </c>
       <c r="S10" t="n">
-        <v>0.7553</v>
+        <v>0.305</v>
       </c>
       <c r="T10" t="n">
-        <v>0.8891</v>
+        <v>0.2602</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1338</v>
+        <v>0.0448</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.3144</v>
+        <v>1.2594</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.3144</v>
+        <v>0.0005</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ALVAREZ RICO</t>
+          <t>M. MURILLO PONS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.4795</v>
+        <v>-0.2211</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7766</v>
+        <v>-1.6684</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2971</v>
+        <v>1.4473</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3081</v>
+        <v>-1.2058</v>
       </c>
       <c r="H11" t="n">
-        <v>0.4614</v>
+        <v>-0.2257</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7695</v>
+        <v>-0.9801</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1816</v>
+        <v>-1.2614</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7514999999999999</v>
+        <v>0.0644</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5699</v>
+        <v>-1.3258</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4897</v>
+        <v>0.0556</v>
       </c>
       <c r="N11" t="n">
         <v>-0.2901</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1996</v>
+        <v>0.3457</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.297</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.9646</v>
+        <v>-1.1117</v>
       </c>
       <c r="R11" t="n">
         <v>1.6676</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1338</v>
+        <v>0.7433</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2524</v>
+        <v>0.7048</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1186</v>
+        <v>0.0385</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2594</v>
+        <v>-0.3144</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0005</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.1663</v>
+        <v>-2.2909</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.9549</v>
+        <v>-1.3011</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.2114</v>
+        <v>-0.9898</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8114</v>
@@ -1390,13 +1390,13 @@
         <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8546</v>
+        <v>0.0208</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3619</v>
+        <v>0.2919</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4927</v>
+        <v>-0.2711</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9444</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>19.6774</v>
+        <v>20.7717</v>
       </c>
       <c r="E13" t="n">
-        <v>3.115699999999999</v>
+        <v>4.210000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>16.5617</v>
+        <v>16.5616</v>
       </c>
       <c r="G13" t="n">
         <v>11.4736</v>
@@ -1468,13 +1468,13 @@
         <v>21.3079</v>
       </c>
       <c r="S13" t="n">
-        <v>0.4413999999999998</v>
+        <v>1.5356</v>
       </c>
       <c r="T13" t="n">
-        <v>3.2272</v>
+        <v>4.3213</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.7859</v>
+        <v>-2.7857</v>
       </c>
       <c r="V13" t="n">
         <v>2.2039</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.3091</v>
+        <v>5.5864</v>
       </c>
       <c r="E14" t="n">
-        <v>2.5918</v>
+        <v>2.396</v>
       </c>
       <c r="F14" t="n">
-        <v>3.7172</v>
+        <v>3.1905</v>
       </c>
       <c r="G14" t="n">
         <v>0.8536</v>
@@ -1546,13 +1546,13 @@
         <v>2.9646</v>
       </c>
       <c r="S14" t="n">
-        <v>1.529</v>
+        <v>0.8064</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8519</v>
+        <v>0.656</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6772</v>
+        <v>0.1504</v>
       </c>
       <c r="V14" t="n">
         <v>1.8883</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.557</v>
+        <v>2.8869</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7493</v>
+        <v>0.9658</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8077</v>
+        <v>1.9211</v>
       </c>
       <c r="G15" t="n">
         <v>3.662</v>
@@ -1624,13 +1624,13 @@
         <v>1.8529</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2868</v>
+        <v>0.6168</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2896</v>
+        <v>0.5061</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0028</v>
+        <v>0.1106</v>
       </c>
       <c r="V15" t="n">
         <v>1.5727</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FERNÁNDEZ HERNÁNDEZ</t>
+          <t>G. PEREZ CABRERA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2441</v>
+        <v>1.8245</v>
       </c>
       <c r="E16" t="n">
-        <v>1.2441</v>
+        <v>0.7214</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1.1031</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2441</v>
+        <v>1.0681</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>0.9285</v>
       </c>
       <c r="I16" t="n">
-        <v>1.2441</v>
+        <v>0.1396</v>
       </c>
       <c r="J16" t="n">
-        <v>1.2441</v>
+        <v>1.7868</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1.8163</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2441</v>
+        <v>-0.0295</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-0.7187</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.8878</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>0.1692</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>0.3706</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.0382</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.4087</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.2431</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.3439</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.587</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.6289</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PEREZ CABRERA</t>
+          <t>J. FERNÁNDEZ HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5915</v>
+        <v>1.2441</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2579</v>
+        <v>1.2441</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8494</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>1.0681</v>
+        <v>1.2441</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9285</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1396</v>
+        <v>1.2441</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7868</v>
+        <v>1.2441</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8163</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.0295</v>
+        <v>1.2441</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.7187</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8878</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1692</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.0382</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.4087</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.4761</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.6354</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8406</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.6289</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.278</v>
+        <v>0.6536999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1553</v>
+        <v>0.0406</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4333</v>
+        <v>0.6131</v>
       </c>
       <c r="G18" t="n">
         <v>1.0576</v>
@@ -1858,13 +1858,13 @@
         <v>1.297</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8177</v>
+        <v>-0.4421</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2524</v>
+        <v>-0.0566</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5653</v>
+        <v>-0.3855</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2589</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.171</v>
+        <v>-0.525</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.6437</v>
+        <v>-2.3499</v>
       </c>
       <c r="F19" t="n">
-        <v>1.4728</v>
+        <v>1.8249</v>
       </c>
       <c r="G19" t="n">
         <v>0.4749</v>
@@ -1936,13 +1936,13 @@
         <v>1.6676</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9428</v>
+        <v>-0.2969</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4166</v>
+        <v>-0.1228</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5263</v>
+        <v>-0.1741</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2589</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.5746</v>
+        <v>-1.2316</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7923</v>
+        <v>-1.4985</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2177</v>
+        <v>0.2669</v>
       </c>
       <c r="G20" t="n">
         <v>1.0946</v>
@@ -2014,13 +2014,13 @@
         <v>0.9264</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5019</v>
+        <v>-0.1589</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.383</v>
+        <v>-0.0892</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.1189</v>
+        <v>-0.0696</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3144</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4722</v>
+        <v>-3.4677</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.6826</v>
+        <v>-0.8012</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7896</v>
+        <v>-2.6665</v>
       </c>
       <c r="G21" t="n">
         <v>-3.8357</v>
@@ -2092,13 +2092,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8779</v>
+        <v>0.1265</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5471</v>
+        <v>0.3342</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3308</v>
+        <v>-0.2077</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3144</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.968</v>
+        <v>-6.8436</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.5735</v>
+        <v>-3.8259</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.3945</v>
+        <v>-3.0177</v>
       </c>
       <c r="G22" t="n">
         <v>-5.3146</v>
@@ -2170,13 +2170,13 @@
         <v>1.4823</v>
       </c>
       <c r="S22" t="n">
-        <v>3.0877</v>
+        <v>1.2121</v>
       </c>
       <c r="T22" t="n">
-        <v>3.7157</v>
+        <v>1.4634</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.628</v>
+        <v>-0.2512</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2589</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. QUINTA RAMOS</t>
+          <t>J. FERNANDEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-9.720499999999999</v>
+        <v>-9.1706</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3297</v>
+        <v>-8.516</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.3908</v>
+        <v>-0.6546</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.9582</v>
+        <v>-7.8199</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.8447</v>
+        <v>-3.9537</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1136</v>
+        <v>-3.8663</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.5256</v>
+        <v>-5.2677</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2198</v>
+        <v>-1.5164</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.3057</v>
+        <v>-3.7513</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.4327</v>
+        <v>-2.5522</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.6248</v>
+        <v>-2.4373</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1922</v>
+        <v>-0.115</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.4823</v>
+        <v>-2.594</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.0382</v>
+        <v>-4.6322</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5558999999999999</v>
+        <v>2.0382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1329</v>
+        <v>-0.0155</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.766</v>
+        <v>0.125</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3669</v>
+        <v>-0.1405</v>
       </c>
       <c r="V23" t="n">
-        <v>-3.1471</v>
+        <v>1.2589</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X23" t="n">
-        <v>-3.1471</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>J. FERNANDEZ HERNANDEZ</t>
+          <t>J. QUINTA RAMOS</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-9.7507</v>
+        <v>-9.328799999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>-8.7119</v>
+        <v>-4.938</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.0389</v>
+        <v>-4.3908</v>
       </c>
       <c r="G24" t="n">
-        <v>-7.8199</v>
+        <v>-3.9582</v>
       </c>
       <c r="H24" t="n">
-        <v>-3.9537</v>
+        <v>-2.8447</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.8663</v>
+        <v>-1.1136</v>
       </c>
       <c r="J24" t="n">
-        <v>-5.2677</v>
+        <v>-2.5256</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.5164</v>
+        <v>-1.2198</v>
       </c>
       <c r="L24" t="n">
-        <v>-3.7513</v>
+        <v>-1.3057</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.5522</v>
+        <v>-1.4327</v>
       </c>
       <c r="N24" t="n">
-        <v>-2.4373</v>
+        <v>-1.6248</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.115</v>
+        <v>0.1922</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.594</v>
+        <v>-1.4823</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.6322</v>
+        <v>-2.0382</v>
       </c>
       <c r="R24" t="n">
-        <v>2.0382</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5956</v>
+        <v>-0.7411</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0709</v>
+        <v>-0.3743</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.5248</v>
+        <v>-0.3669</v>
       </c>
       <c r="V24" t="n">
-        <v>1.2589</v>
+        <v>-3.1471</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-3.1471</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-19.6773</v>
+        <v>-18.3717</v>
       </c>
       <c r="E25" t="n">
-        <v>-16.5617</v>
+        <v>-16.5616</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.115699999999999</v>
+        <v>-1.81</v>
       </c>
       <c r="G25" t="n">
         <v>-11.4735</v>
@@ -2404,13 +2404,13 @@
         <v>15.7495</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.4414000000000001</v>
+        <v>0.8642</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7858</v>
+        <v>2.7857</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.2272</v>
+        <v>-1.9215</v>
       </c>
       <c r="V25" t="n">
         <v>-2.2038</v>
